--- a/InputData/land/FoFObE/Fraction of Forests Owned by Entity.xlsx
+++ b/InputData/land/FoFObE/Fraction of Forests Owned by Entity.xlsx
@@ -1,28 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23801"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jonah\Documents\EPS Model\Test\.USE THIS TO TEST\InputData\land\FoFObE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\land\FoFObE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B305FAA-C9C8-417A-91E4-BC3B025F465D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D0EA2B-02FF-453F-9596-BFD3D1EA0E4A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1485" yWindow="1425" windowWidth="13560" windowHeight="13575" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9150" yWindow="690" windowWidth="29520" windowHeight="21060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="FoFObE" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
   <si>
     <t>FoFObE Fraction of Forests Owned by Entity</t>
   </si>
@@ -38,85 +41,73 @@
     <t>Source:</t>
   </si>
   <si>
-    <t>Fraction of Forest Owned</t>
+    <t>National Forest</t>
+  </si>
+  <si>
+    <t>Other public</t>
+  </si>
+  <si>
+    <t>Forest industry</t>
+  </si>
+  <si>
+    <t>Other private</t>
+  </si>
+  <si>
+    <t>Timber land</t>
+  </si>
+  <si>
+    <t>Reserved forest</t>
+  </si>
+  <si>
+    <t>Other forest</t>
+  </si>
+  <si>
+    <t>U.S.</t>
+  </si>
+  <si>
+    <t>Ownership of Forest Land (million hectares)</t>
+  </si>
+  <si>
+    <t>U.S. Forest Service</t>
+  </si>
+  <si>
+    <t>U.S. Forest Facts and Historical Trends</t>
+  </si>
+  <si>
+    <t>http://www.fia.fs.fed.us/library/briefings-summaries-overviews/docs/ForestFactsMetric.pdf</t>
+  </si>
+  <si>
+    <t>Page 6</t>
   </si>
   <si>
     <t>government</t>
   </si>
   <si>
-    <t xml:space="preserve">Ownership of Forest Land </t>
-  </si>
-  <si>
-    <t>Government share</t>
-  </si>
-  <si>
-    <t>Consumers/households</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>USDA and U.S. Forest Service</t>
-  </si>
-  <si>
-    <t>Forests of Oregon</t>
-  </si>
-  <si>
-    <t>https://usfs.maps.arcgis.com/apps/MapJournal/index.html?appid=0c0d40567089480684aedcceb88387eb#</t>
-  </si>
-  <si>
-    <t>Oregon Forest Land Ownership</t>
-  </si>
-  <si>
-    <t>Section: Ownership</t>
-  </si>
-  <si>
-    <t>National Forests</t>
-  </si>
-  <si>
-    <t>Bureau of Land Mgmt.</t>
-  </si>
-  <si>
-    <t>Other Federal</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>County-Municipal</t>
-  </si>
-  <si>
-    <t>Private Corporate</t>
-  </si>
-  <si>
-    <t>Private Noncorporate</t>
-  </si>
-  <si>
-    <t>nonenergy industries</t>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>The amount of government-owned forest is provided in the table.</t>
+  </si>
+  <si>
+    <t>We assume that all privately-owned forest used for timber land is owned</t>
+  </si>
+  <si>
+    <t>by industry, and half of the remaining privately-owned forest land is owned</t>
+  </si>
+  <si>
+    <t>by industry.  The remainder is owned by consumers.</t>
+  </si>
+  <si>
+    <t>foreign entities</t>
   </si>
   <si>
     <t>labor and consumers</t>
   </si>
   <si>
-    <t>foreign entities</t>
-  </si>
-  <si>
-    <t>electricity suppliers</t>
-  </si>
-  <si>
-    <t>coal suppliers</t>
-  </si>
-  <si>
-    <t>natural gas and petroleum suppliers</t>
-  </si>
-  <si>
-    <t>biomass and biofuel suppliers</t>
-  </si>
-  <si>
-    <t>other energy suppliers</t>
-  </si>
-  <si>
-    <t>total</t>
+    <t>Fraction of Forest Owned (dimensionless)</t>
+  </si>
+  <si>
+    <t>domestic industries</t>
   </si>
 </sst>
 </file>
@@ -126,7 +117,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,25 +141,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -187,14 +166,20 @@
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -211,72 +196,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>501315</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFE80864-4194-43A9-AACA-30C653601507}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2762250" y="152400"/>
-          <a:ext cx="5416215" cy="4229099"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -600,11 +519,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="28.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -615,41 +531,58 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>8</v>
+      <c r="B4" s="3">
+        <v>2001</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="6">
-        <v>2016</v>
+      <c r="B5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>9</v>
+      <c r="B6" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>12</v>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" display="https://usfs.maps.arcgis.com/apps/MapJournal/index.html?appid=0c0d40567089480684aedcceb88387eb" xr:uid="{3315A321-9227-4349-8D9B-23E7D2E0195B}"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
@@ -658,115 +591,153 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11">
-        <v>0.14000000000000001</v>
+      <c r="B11" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16">
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22">
-        <f>SUM(B3:B7)</f>
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23">
-        <f>B11</f>
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B24">
-        <f>B9</f>
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="7">
-        <f>SUM(B22:B24)</f>
-        <v>1</v>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -775,90 +746,50 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
     <col min="2" max="2" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>2</v>
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B1" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3">
-        <f>Data!$B$22</f>
-        <v>0.64</v>
+        <v>15</v>
+      </c>
+      <c r="B2" s="5">
+        <f>SUM(Data!B3,Data!B7)/SUM(Data!B3,Data!B7,Data!B11,Data!B15)</f>
+        <v>0.42384105960264901</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="3">
-        <f>Data!$B$23</f>
-        <v>0.14000000000000001</v>
+        <v>24</v>
+      </c>
+      <c r="B3" s="5">
+        <f>SUM(Data!B11,Data!B16,Data!B18/2)/SUM(Data!B3,Data!B7,Data!B11,Data!B15)</f>
+        <v>0.52814569536423839</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="3">
-        <f>Data!$B$24</f>
-        <v>0.22</v>
+        <v>22</v>
+      </c>
+      <c r="B4" s="5">
+        <f>(Data!B18/2)/SUM(Data!B3,Data!B7,Data!B11,Data!B15)</f>
+        <v>4.8013245033112585E-2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10">
         <v>0</v>
       </c>
     </row>
